--- a/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{562F117F-6D61-44D4-9E33-84E5B532C402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8793A9F6-E5E5-4D69-9F06-98323A25F4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,22 +763,28 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ARE_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ARE_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
+    <t>distr_solelc_spv_ARE_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_solelc_spv_ARE_002</t>
@@ -823,22 +829,19 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ARE_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE,e_w181353370-220_ARE</t>
+  </si>
+  <si>
     <t>e_w94950821-400_ARE,e_w181332757-400_ARE,e_w29495157-400_ARE</t>
   </si>
   <si>
-    <t>e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE,e_w181353370-220_ARE</t>
+    <t>e_w1225109215-400_ARE,e_w29504133-220_ARE,e_w95046964-220_ARE</t>
   </si>
   <si>
     <t>e_w309146009-400_ARE,e_w1264993337-400_ARE,e_AE27-400_ARE,e_w301647038-400_ARE</t>
@@ -862,7 +865,40 @@
     <t>e_AE32-220_ARE,e_w301690692-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_AE37-400_ARE,e_w1264942732-220_ARE</t>
   </si>
   <si>
-    <t>e_w1225109215-400_ARE,e_w29504133-220_ARE,e_w95046964-220_ARE</t>
+    <t>distr_wonelc_won_ARE_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_ARE_005</t>
@@ -877,12 +913,6 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ARE_003</t>
   </si>
   <si>
@@ -895,34 +925,40 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
+    <t>elc_won_ARE_001</t>
+  </si>
+  <si>
+    <t>e_w132159930-220_ARE,e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_002</t>
+  </si>
+  <si>
+    <t>e_w132159930-220_ARE,e_w309146009-400_ARE,e_AE33-220_ARE,e_w1264993337-400_ARE,e_AE32-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_004</t>
+  </si>
+  <si>
+    <t>e_AE27-400_ARE,e_w301647038-400_ARE,e_w301690692-220_ARE,e_w526194855-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_w1264942732-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_007</t>
+  </si>
+  <si>
+    <t>e_w181332757-400_ARE,e_w29495157-400_ARE,e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_006</t>
+  </si>
+  <si>
+    <t>e_w260963603-400_ARE</t>
   </si>
   <si>
     <t>elc_won_ARE_005</t>
@@ -937,12 +973,6 @@
     <t>e_w95046964-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE</t>
   </si>
   <si>
-    <t>elc_won_ARE_001</t>
-  </si>
-  <si>
-    <t>e_w132159930-220_ARE,e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE</t>
-  </si>
-  <si>
     <t>elc_won_ARE_003</t>
   </si>
   <si>
@@ -953,36 +983,6 @@
   </si>
   <si>
     <t>e_AE20-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_007</t>
-  </si>
-  <si>
-    <t>e_w181332757-400_ARE,e_w29495157-400_ARE,e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_006</t>
-  </si>
-  <si>
-    <t>e_w260963603-400_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_002</t>
-  </si>
-  <si>
-    <t>e_w132159930-220_ARE,e_w309146009-400_ARE,e_AE33-220_ARE,e_w1264993337-400_ARE,e_AE32-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_004</t>
-  </si>
-  <si>
-    <t>e_AE27-400_ARE,e_w301647038-400_ARE,e_w301690692-220_ARE,e_w526194855-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_w1264942732-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ARE_001</t>
@@ -2383,6 +2383,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -6161,7 +6164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{565DC168-4236-450E-B1BC-24C500A4F625}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82137E4E-D38E-4211-BB5D-F32E12783EAE}">
   <dimension ref="B9:BD20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6399,16 +6402,16 @@
         <v>211</v>
       </c>
       <c r="Y11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z11" t="s">
         <v>235</v>
       </c>
       <c r="AA11">
-        <v>0.99924944940200633</v>
+        <v>0.99710584239916322</v>
       </c>
       <c r="AB11">
-        <v>13.760094296550193</v>
+        <v>53.059556015340199</v>
       </c>
       <c r="AD11" t="s">
         <v>210</v>
@@ -6441,10 +6444,10 @@
         <v>266</v>
       </c>
       <c r="AO11">
-        <v>0.998734612165461</v>
+        <v>0.99635525152088078</v>
       </c>
       <c r="AP11">
-        <v>23.198776966549204</v>
+        <v>66.820388783853375</v>
       </c>
       <c r="AR11" t="s">
         <v>210</v>
@@ -6545,16 +6548,16 @@
         <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Z12" t="s">
         <v>236</v>
       </c>
       <c r="AA12">
-        <v>0.99710584239916322</v>
+        <v>0.99924944940200633</v>
       </c>
       <c r="AB12">
-        <v>53.059556015340199</v>
+        <v>13.760094296550193</v>
       </c>
       <c r="AD12" t="s">
         <v>210</v>
@@ -6587,10 +6590,10 @@
         <v>268</v>
       </c>
       <c r="AO12">
-        <v>0.99873143865369307</v>
+        <v>0.99911949794866695</v>
       </c>
       <c r="AP12">
-        <v>23.25695801562755</v>
+        <v>16.142537607772773</v>
       </c>
       <c r="AR12" t="s">
         <v>210</v>
@@ -6691,16 +6694,16 @@
         <v>217</v>
       </c>
       <c r="Y13" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Z13" t="s">
         <v>237</v>
       </c>
       <c r="AA13">
-        <v>0.9975822055979704</v>
+        <v>0.99870476779891471</v>
       </c>
       <c r="AB13">
-        <v>44.326230703875503</v>
+        <v>23.745923686563614</v>
       </c>
       <c r="AD13" t="s">
         <v>210</v>
@@ -6733,10 +6736,10 @@
         <v>270</v>
       </c>
       <c r="AO13">
-        <v>0.99635525152088078</v>
+        <v>0.99889524579767786</v>
       </c>
       <c r="AP13">
-        <v>66.820388783853375</v>
+        <v>20.253827042572624</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6801,16 +6804,16 @@
         <v>219</v>
       </c>
       <c r="Y14" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="Z14" t="s">
         <v>238</v>
       </c>
       <c r="AA14">
-        <v>0.99883020545500567</v>
+        <v>0.9975822055979704</v>
       </c>
       <c r="AB14">
-        <v>21.446233324896248</v>
+        <v>44.326230703875503</v>
       </c>
       <c r="AD14" t="s">
         <v>210</v>
@@ -6843,10 +6846,10 @@
         <v>272</v>
       </c>
       <c r="AO14">
-        <v>0.99880354308642672</v>
+        <v>0.99906614193740051</v>
       </c>
       <c r="AP14">
-        <v>21.935043415510535</v>
+        <v>17.120731147657697</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6911,16 +6914,16 @@
         <v>221</v>
       </c>
       <c r="Y15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z15" t="s">
         <v>239</v>
       </c>
       <c r="AA15">
-        <v>0.99872710412225529</v>
+        <v>0.99883020545500567</v>
       </c>
       <c r="AB15">
-        <v>23.336424425319287</v>
+        <v>21.446233324896248</v>
       </c>
       <c r="AD15" t="s">
         <v>210</v>
@@ -6953,10 +6956,10 @@
         <v>274</v>
       </c>
       <c r="AO15">
-        <v>0.99840816948494737</v>
+        <v>0.99793473720944781</v>
       </c>
       <c r="AP15">
-        <v>29.183559442632479</v>
+        <v>37.863151160123977</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7021,16 +7024,16 @@
         <v>223</v>
       </c>
       <c r="Y16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Z16" t="s">
         <v>240</v>
       </c>
       <c r="AA16">
-        <v>0.99914104512082091</v>
+        <v>0.99872710412225529</v>
       </c>
       <c r="AB16">
-        <v>15.747506118283479</v>
+        <v>23.336424425319287</v>
       </c>
       <c r="AD16" t="s">
         <v>210</v>
@@ -7063,10 +7066,10 @@
         <v>276</v>
       </c>
       <c r="AO16">
-        <v>0.99906614193740051</v>
+        <v>0.99806854175718718</v>
       </c>
       <c r="AP16">
-        <v>17.120731147657697</v>
+        <v>35.410067784902452</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -7131,16 +7134,16 @@
         <v>225</v>
       </c>
       <c r="Y17" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Z17" t="s">
         <v>241</v>
       </c>
       <c r="AA17">
-        <v>0.9976461542275985</v>
+        <v>0.99914104512082091</v>
       </c>
       <c r="AB17">
-        <v>43.153839160693863</v>
+        <v>15.747506118283479</v>
       </c>
       <c r="AD17" t="s">
         <v>210</v>
@@ -7173,10 +7176,10 @@
         <v>278</v>
       </c>
       <c r="AO17">
-        <v>0.99806854175718718</v>
+        <v>0.998734612165461</v>
       </c>
       <c r="AP17">
-        <v>35.410067784902452</v>
+        <v>23.198776966549204</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7241,16 +7244,16 @@
         <v>227</v>
       </c>
       <c r="Y18" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s">
         <v>242</v>
       </c>
       <c r="AA18">
-        <v>0.99759397813724437</v>
+        <v>0.9976461542275985</v>
       </c>
       <c r="AB18">
-        <v>44.110400817185507</v>
+        <v>43.153839160693863</v>
       </c>
       <c r="AD18" t="s">
         <v>210</v>
@@ -7283,10 +7286,10 @@
         <v>280</v>
       </c>
       <c r="AO18">
-        <v>0.99911949794866695</v>
+        <v>0.99873143865369307</v>
       </c>
       <c r="AP18">
-        <v>16.142537607772773</v>
+        <v>23.25695801562755</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7351,16 +7354,16 @@
         <v>229</v>
       </c>
       <c r="Y19" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Z19" t="s">
         <v>243</v>
       </c>
       <c r="AA19">
-        <v>0.99890511709712682</v>
+        <v>0.99759397813724437</v>
       </c>
       <c r="AB19">
-        <v>20.072853219340832</v>
+        <v>44.110400817185507</v>
       </c>
       <c r="AD19" t="s">
         <v>210</v>
@@ -7393,10 +7396,10 @@
         <v>282</v>
       </c>
       <c r="AO19">
-        <v>0.99889524579767786</v>
+        <v>0.99880354308642672</v>
       </c>
       <c r="AP19">
-        <v>20.253827042572624</v>
+        <v>21.935043415510535</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7461,16 +7464,16 @@
         <v>231</v>
       </c>
       <c r="Y20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="Z20" t="s">
         <v>244</v>
       </c>
       <c r="AA20">
-        <v>0.99870476779891471</v>
+        <v>0.99890511709712682</v>
       </c>
       <c r="AB20">
-        <v>23.745923686563614</v>
+        <v>20.072853219340832</v>
       </c>
       <c r="AD20" t="s">
         <v>210</v>
@@ -7503,10 +7506,10 @@
         <v>284</v>
       </c>
       <c r="AO20">
-        <v>0.99793473720944781</v>
+        <v>0.99840816948494737</v>
       </c>
       <c r="AP20">
-        <v>37.863151160123977</v>
+        <v>29.183559442632479</v>
       </c>
     </row>
   </sheetData>
@@ -7515,7 +7518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9762B8-C301-4724-8A32-E2534A947093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B8723A-8E58-4054-919F-DA2FBDFEAD2E}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7627,7 +7630,7 @@
         <v>292</v>
       </c>
       <c r="K11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L11">
         <v>9.9944870858215555</v>
@@ -7695,7 +7698,7 @@
         <v>294</v>
       </c>
       <c r="K12" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="L12">
         <v>5.4764817961853396</v>
@@ -7763,7 +7766,7 @@
         <v>296</v>
       </c>
       <c r="K13" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="L13">
         <v>19.136132966435476</v>
@@ -7798,7 +7801,7 @@
         <v>298</v>
       </c>
       <c r="K14" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="L14">
         <v>3.9432065697252274</v>
@@ -7833,7 +7836,7 @@
         <v>300</v>
       </c>
       <c r="K15" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="L15">
         <v>5.3471227572163897</v>
@@ -7868,7 +7871,7 @@
         <v>302</v>
       </c>
       <c r="K16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L16">
         <v>4.1115133977210352</v>
@@ -7903,7 +7906,7 @@
         <v>304</v>
       </c>
       <c r="K17" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L17">
         <v>4.0168479649465931</v>
@@ -7938,7 +7941,7 @@
         <v>306</v>
       </c>
       <c r="K18" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="L18">
         <v>5.3548842938803451</v>
@@ -7973,7 +7976,7 @@
         <v>308</v>
       </c>
       <c r="K19" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="L19">
         <v>6.4642612617009894</v>
@@ -8008,7 +8011,7 @@
         <v>310</v>
       </c>
       <c r="K20" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L20">
         <v>6.5113691354542258</v>
@@ -8023,7 +8026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C195CDDF-108F-45B0-B8F7-E48C7ADF317D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1B5468-1F42-45F7-9221-F87C5BA10D68}">
   <dimension ref="B9:P64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9579,7 +9582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E42208-E6EF-4E3B-A010-92AA122EB872}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF846C9-C311-412C-9333-F7E3EC99CAD4}">
   <dimension ref="B2:M35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8793A9F6-E5E5-4D69-9F06-98323A25F4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB3DC3FF-7239-404F-B4F5-7E42E2C88D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,60 +763,60 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ARE_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ARE_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ARE_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ARE_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ARE_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ARE_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ARE_001</t>
   </si>
   <si>
@@ -835,52 +835,58 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w309146009-400_ARE,e_w1264993337-400_ARE,e_AE27-400_ARE,e_w301647038-400_ARE</t>
+  </si>
+  <si>
+    <t>e_AE39-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE,e_AE20-220_ARE</t>
+  </si>
+  <si>
+    <t>e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE,e_w260963603-400_ARE</t>
+  </si>
+  <si>
     <t>e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE,e_w181353370-220_ARE</t>
   </si>
   <si>
     <t>e_w94950821-400_ARE,e_w181332757-400_ARE,e_w29495157-400_ARE</t>
   </si>
   <si>
+    <t>e_w395805805-220_ARE,e_w95099973-220_ARE,e_AE40-220_ARE,e_AE42-220_ARE,e_w301715569-220_ARE</t>
+  </si>
+  <si>
+    <t>e_w301663552-220_ARE,e_w181361589-220_ARE,e_w132159924-220_ARE</t>
+  </si>
+  <si>
     <t>e_w1225109215-400_ARE,e_w29504133-220_ARE,e_w95046964-220_ARE</t>
   </si>
   <si>
-    <t>e_w309146009-400_ARE,e_w1264993337-400_ARE,e_AE27-400_ARE,e_w301647038-400_ARE</t>
-  </si>
-  <si>
-    <t>e_AE39-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE,e_AE20-220_ARE</t>
-  </si>
-  <si>
-    <t>e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE,e_w260963603-400_ARE</t>
-  </si>
-  <si>
-    <t>e_w395805805-220_ARE,e_w95099973-220_ARE,e_AE40-220_ARE,e_AE42-220_ARE,e_w301715569-220_ARE</t>
-  </si>
-  <si>
-    <t>e_w301663552-220_ARE,e_w181361589-220_ARE,e_w132159924-220_ARE</t>
-  </si>
-  <si>
     <t>e_w132159930-220_ARE,e_AE33-220_ARE</t>
   </si>
   <si>
     <t>e_AE32-220_ARE,e_w301690692-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_AE37-400_ARE,e_w1264942732-220_ARE</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ARE_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ARE_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_ARE_007</t>
@@ -889,10 +895,16 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
+    <t>distr_wonelc_won_ARE_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_ARE_006</t>
@@ -901,18 +913,6 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ARE_003</t>
   </si>
   <si>
@@ -925,22 +925,28 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_won_ARE_002</t>
+  </si>
+  <si>
+    <t>e_w132159930-220_ARE,e_w309146009-400_ARE,e_AE33-220_ARE,e_w1264993337-400_ARE,e_AE32-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_004</t>
+  </si>
+  <si>
+    <t>e_AE27-400_ARE,e_w301647038-400_ARE,e_w301690692-220_ARE,e_w526194855-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_w1264942732-220_ARE</t>
+  </si>
+  <si>
     <t>elc_won_ARE_001</t>
   </si>
   <si>
     <t>e_w132159930-220_ARE,e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE</t>
   </si>
   <si>
-    <t>elc_won_ARE_002</t>
-  </si>
-  <si>
-    <t>e_w132159930-220_ARE,e_w309146009-400_ARE,e_AE33-220_ARE,e_w1264993337-400_ARE,e_AE32-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_004</t>
-  </si>
-  <si>
-    <t>e_AE27-400_ARE,e_w301647038-400_ARE,e_w301690692-220_ARE,e_w526194855-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_w1264942732-220_ARE</t>
+    <t>elc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
   </si>
   <si>
     <t>elc_won_ARE_007</t>
@@ -949,28 +955,22 @@
     <t>e_w181332757-400_ARE,e_w29495157-400_ARE,e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE</t>
   </si>
   <si>
-    <t>elc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
+    <t>elc_won_ARE_005</t>
+  </si>
+  <si>
+    <t>e_AE37-400_ARE,e_w94950821-400_ARE,e_w1225109215-400_ARE,e_w29504133-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_010</t>
+  </si>
+  <si>
+    <t>e_w95046964-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE</t>
   </si>
   <si>
     <t>elc_won_ARE_006</t>
   </si>
   <si>
     <t>e_w260963603-400_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_005</t>
-  </si>
-  <si>
-    <t>e_AE37-400_ARE,e_w94950821-400_ARE,e_w1225109215-400_ARE,e_w29504133-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_010</t>
-  </si>
-  <si>
-    <t>e_w95046964-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE</t>
   </si>
   <si>
     <t>elc_won_ARE_003</t>
@@ -6164,7 +6164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82137E4E-D38E-4211-BB5D-F32E12783EAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11C2703-82A6-4CC8-856B-0F796B0DE245}">
   <dimension ref="B9:BD20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6402,16 +6402,16 @@
         <v>211</v>
       </c>
       <c r="Y11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Z11" t="s">
         <v>235</v>
       </c>
       <c r="AA11">
-        <v>0.99710584239916322</v>
+        <v>0.9975822055979704</v>
       </c>
       <c r="AB11">
-        <v>53.059556015340199</v>
+        <v>44.326230703875503</v>
       </c>
       <c r="AD11" t="s">
         <v>210</v>
@@ -6444,10 +6444,10 @@
         <v>266</v>
       </c>
       <c r="AO11">
-        <v>0.99635525152088078</v>
+        <v>0.99911949794866695</v>
       </c>
       <c r="AP11">
-        <v>66.820388783853375</v>
+        <v>16.142537607772773</v>
       </c>
       <c r="AR11" t="s">
         <v>210</v>
@@ -6548,16 +6548,16 @@
         <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z12" t="s">
         <v>236</v>
       </c>
       <c r="AA12">
-        <v>0.99924944940200633</v>
+        <v>0.99883020545500567</v>
       </c>
       <c r="AB12">
-        <v>13.760094296550193</v>
+        <v>21.446233324896248</v>
       </c>
       <c r="AD12" t="s">
         <v>210</v>
@@ -6590,10 +6590,10 @@
         <v>268</v>
       </c>
       <c r="AO12">
-        <v>0.99911949794866695</v>
+        <v>0.99889524579767786</v>
       </c>
       <c r="AP12">
-        <v>16.142537607772773</v>
+        <v>20.253827042572624</v>
       </c>
       <c r="AR12" t="s">
         <v>210</v>
@@ -6694,16 +6694,16 @@
         <v>217</v>
       </c>
       <c r="Y13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Z13" t="s">
         <v>237</v>
       </c>
       <c r="AA13">
-        <v>0.99870476779891471</v>
+        <v>0.99872710412225529</v>
       </c>
       <c r="AB13">
-        <v>23.745923686563614</v>
+        <v>23.336424425319287</v>
       </c>
       <c r="AD13" t="s">
         <v>210</v>
@@ -6736,10 +6736,10 @@
         <v>270</v>
       </c>
       <c r="AO13">
-        <v>0.99889524579767786</v>
+        <v>0.99635525152088078</v>
       </c>
       <c r="AP13">
-        <v>20.253827042572624</v>
+        <v>66.820388783853375</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6804,16 +6804,16 @@
         <v>219</v>
       </c>
       <c r="Y14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Z14" t="s">
         <v>238</v>
       </c>
       <c r="AA14">
-        <v>0.9975822055979704</v>
+        <v>0.99710584239916322</v>
       </c>
       <c r="AB14">
-        <v>44.326230703875503</v>
+        <v>53.059556015340199</v>
       </c>
       <c r="AD14" t="s">
         <v>210</v>
@@ -6846,10 +6846,10 @@
         <v>272</v>
       </c>
       <c r="AO14">
-        <v>0.99906614193740051</v>
+        <v>0.99793473720944781</v>
       </c>
       <c r="AP14">
-        <v>17.120731147657697</v>
+        <v>37.863151160123977</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6914,16 +6914,16 @@
         <v>221</v>
       </c>
       <c r="Y15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Z15" t="s">
         <v>239</v>
       </c>
       <c r="AA15">
-        <v>0.99883020545500567</v>
+        <v>0.99924944940200633</v>
       </c>
       <c r="AB15">
-        <v>21.446233324896248</v>
+        <v>13.760094296550193</v>
       </c>
       <c r="AD15" t="s">
         <v>210</v>
@@ -6956,10 +6956,10 @@
         <v>274</v>
       </c>
       <c r="AO15">
-        <v>0.99793473720944781</v>
+        <v>0.99906614193740051</v>
       </c>
       <c r="AP15">
-        <v>37.863151160123977</v>
+        <v>17.120731147657697</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7024,16 +7024,16 @@
         <v>223</v>
       </c>
       <c r="Y16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Z16" t="s">
         <v>240</v>
       </c>
       <c r="AA16">
-        <v>0.99872710412225529</v>
+        <v>0.99914104512082091</v>
       </c>
       <c r="AB16">
-        <v>23.336424425319287</v>
+        <v>15.747506118283479</v>
       </c>
       <c r="AD16" t="s">
         <v>210</v>
@@ -7066,10 +7066,10 @@
         <v>276</v>
       </c>
       <c r="AO16">
-        <v>0.99806854175718718</v>
+        <v>0.998734612165461</v>
       </c>
       <c r="AP16">
-        <v>35.410067784902452</v>
+        <v>23.198776966549204</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -7134,16 +7134,16 @@
         <v>225</v>
       </c>
       <c r="Y17" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Z17" t="s">
         <v>241</v>
       </c>
       <c r="AA17">
-        <v>0.99914104512082091</v>
+        <v>0.9976461542275985</v>
       </c>
       <c r="AB17">
-        <v>15.747506118283479</v>
+        <v>43.153839160693863</v>
       </c>
       <c r="AD17" t="s">
         <v>210</v>
@@ -7176,10 +7176,10 @@
         <v>278</v>
       </c>
       <c r="AO17">
-        <v>0.998734612165461</v>
+        <v>0.99873143865369307</v>
       </c>
       <c r="AP17">
-        <v>23.198776966549204</v>
+        <v>23.25695801562755</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7244,16 +7244,16 @@
         <v>227</v>
       </c>
       <c r="Y18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s">
         <v>242</v>
       </c>
       <c r="AA18">
-        <v>0.9976461542275985</v>
+        <v>0.99870476779891471</v>
       </c>
       <c r="AB18">
-        <v>43.153839160693863</v>
+        <v>23.745923686563614</v>
       </c>
       <c r="AD18" t="s">
         <v>210</v>
@@ -7286,10 +7286,10 @@
         <v>280</v>
       </c>
       <c r="AO18">
-        <v>0.99873143865369307</v>
+        <v>0.99806854175718718</v>
       </c>
       <c r="AP18">
-        <v>23.25695801562755</v>
+        <v>35.410067784902452</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7518,7 +7518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B8723A-8E58-4054-919F-DA2FBDFEAD2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D34494-0E56-4497-BB26-325067F8E221}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7630,7 +7630,7 @@
         <v>292</v>
       </c>
       <c r="K11" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L11">
         <v>9.9944870858215555</v>
@@ -7698,7 +7698,7 @@
         <v>294</v>
       </c>
       <c r="K12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L12">
         <v>5.4764817961853396</v>
@@ -7801,7 +7801,7 @@
         <v>298</v>
       </c>
       <c r="K14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L14">
         <v>3.9432065697252274</v>
@@ -7836,7 +7836,7 @@
         <v>300</v>
       </c>
       <c r="K15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L15">
         <v>5.3471227572163897</v>
@@ -7871,7 +7871,7 @@
         <v>302</v>
       </c>
       <c r="K16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L16">
         <v>4.1115133977210352</v>
@@ -7906,7 +7906,7 @@
         <v>304</v>
       </c>
       <c r="K17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L17">
         <v>4.0168479649465931</v>
@@ -7976,7 +7976,7 @@
         <v>308</v>
       </c>
       <c r="K19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L19">
         <v>6.4642612617009894</v>
@@ -8011,7 +8011,7 @@
         <v>310</v>
       </c>
       <c r="K20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L20">
         <v>6.5113691354542258</v>
@@ -8026,7 +8026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1B5468-1F42-45F7-9221-F87C5BA10D68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED4C6F5-46E1-42B4-B063-8927587216F8}">
   <dimension ref="B9:P64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9582,7 +9582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF846C9-C311-412C-9333-F7E3EC99CAD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040F5773-FC6C-4D8B-91D8-43D9E0E03C51}">
   <dimension ref="B2:M35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB3DC3FF-7239-404F-B4F5-7E42E2C88D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1932886B-522A-4C60-A434-3BAC698D1E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,18 +763,48 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ARE_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ARE_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ARE_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ARE_008</t>
   </si>
   <si>
@@ -787,18 +817,6 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ARE_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ARE_005</t>
   </si>
   <si>
@@ -811,30 +829,27 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ARE_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ARE_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1225109215-400_ARE,e_w29504133-220_ARE,e_w95046964-220_ARE</t>
+  </si>
+  <si>
+    <t>e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE,e_w181353370-220_ARE</t>
+  </si>
+  <si>
+    <t>e_w94950821-400_ARE,e_w181332757-400_ARE,e_w29495157-400_ARE</t>
+  </si>
+  <si>
+    <t>e_w132159930-220_ARE,e_AE33-220_ARE</t>
+  </si>
+  <si>
+    <t>e_AE32-220_ARE,e_w301690692-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_AE37-400_ARE,e_w1264942732-220_ARE</t>
+  </si>
+  <si>
     <t>e_w309146009-400_ARE,e_w1264993337-400_ARE,e_AE27-400_ARE,e_w301647038-400_ARE</t>
   </si>
   <si>
@@ -844,25 +859,16 @@
     <t>e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE,e_w260963603-400_ARE</t>
   </si>
   <si>
-    <t>e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE,e_w181353370-220_ARE</t>
-  </si>
-  <si>
-    <t>e_w94950821-400_ARE,e_w181332757-400_ARE,e_w29495157-400_ARE</t>
-  </si>
-  <si>
     <t>e_w395805805-220_ARE,e_w95099973-220_ARE,e_AE40-220_ARE,e_AE42-220_ARE,e_w301715569-220_ARE</t>
   </si>
   <si>
     <t>e_w301663552-220_ARE,e_w181361589-220_ARE,e_w132159924-220_ARE</t>
   </si>
   <si>
-    <t>e_w1225109215-400_ARE,e_w29504133-220_ARE,e_w95046964-220_ARE</t>
-  </si>
-  <si>
-    <t>e_w132159930-220_ARE,e_AE33-220_ARE</t>
-  </si>
-  <si>
-    <t>e_AE32-220_ARE,e_w301690692-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_AE37-400_ARE,e_w1264942732-220_ARE</t>
+    <t>distr_wonelc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_ARE_002</t>
@@ -877,42 +883,36 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ARE_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ARE_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ARE_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ARE_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ARE_003</t>
   </si>
   <si>
@@ -925,6 +925,12 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_won_ARE_009</t>
+  </si>
+  <si>
+    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
+  </si>
+  <si>
     <t>elc_won_ARE_002</t>
   </si>
   <si>
@@ -937,40 +943,34 @@
     <t>e_AE27-400_ARE,e_w301647038-400_ARE,e_w301690692-220_ARE,e_w526194855-220_ARE,e_w939814405-220_ARE,e_w526194855-400_ARE,e_w1264942732-220_ARE</t>
   </si>
   <si>
+    <t>elc_won_ARE_006</t>
+  </si>
+  <si>
+    <t>e_w260963603-400_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_007</t>
+  </si>
+  <si>
+    <t>e_w181332757-400_ARE,e_w29495157-400_ARE,e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_005</t>
+  </si>
+  <si>
+    <t>e_AE37-400_ARE,e_w94950821-400_ARE,e_w1225109215-400_ARE,e_w29504133-220_ARE</t>
+  </si>
+  <si>
+    <t>elc_won_ARE_010</t>
+  </si>
+  <si>
+    <t>e_w95046964-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE</t>
+  </si>
+  <si>
     <t>elc_won_ARE_001</t>
   </si>
   <si>
     <t>e_w132159930-220_ARE,e_AE33-220_ARE,e_w395805805-220_ARE,e_w301663553-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_009</t>
-  </si>
-  <si>
-    <t>e_w132159924-220_ARE,e_AE39-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_007</t>
-  </si>
-  <si>
-    <t>e_w181332757-400_ARE,e_w29495157-400_ARE,e_w1255406048-400_ARE,e_AE1-220_ARE,e_w94816851-400_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_005</t>
-  </si>
-  <si>
-    <t>e_AE37-400_ARE,e_w94950821-400_ARE,e_w1225109215-400_ARE,e_w29504133-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_010</t>
-  </si>
-  <si>
-    <t>e_w95046964-220_ARE,e_AE34-220_ARE,e_w95084799-220_ARE</t>
-  </si>
-  <si>
-    <t>elc_won_ARE_006</t>
-  </si>
-  <si>
-    <t>e_w260963603-400_ARE</t>
   </si>
   <si>
     <t>elc_won_ARE_003</t>
@@ -6164,7 +6164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11C2703-82A6-4CC8-856B-0F796B0DE245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE0AB0A5-A122-4193-BAD5-446686B322C0}">
   <dimension ref="B9:BD20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6402,16 +6402,16 @@
         <v>211</v>
       </c>
       <c r="Y11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Z11" t="s">
         <v>235</v>
       </c>
       <c r="AA11">
-        <v>0.9975822055979704</v>
+        <v>0.99870476779891471</v>
       </c>
       <c r="AB11">
-        <v>44.326230703875503</v>
+        <v>23.745923686563614</v>
       </c>
       <c r="AD11" t="s">
         <v>210</v>
@@ -6444,10 +6444,10 @@
         <v>266</v>
       </c>
       <c r="AO11">
-        <v>0.99911949794866695</v>
+        <v>0.99793473720944781</v>
       </c>
       <c r="AP11">
-        <v>16.142537607772773</v>
+        <v>37.863151160123977</v>
       </c>
       <c r="AR11" t="s">
         <v>210</v>
@@ -6548,16 +6548,16 @@
         <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Z12" t="s">
         <v>236</v>
       </c>
       <c r="AA12">
-        <v>0.99883020545500567</v>
+        <v>0.99710584239916322</v>
       </c>
       <c r="AB12">
-        <v>21.446233324896248</v>
+        <v>53.059556015340199</v>
       </c>
       <c r="AD12" t="s">
         <v>210</v>
@@ -6590,10 +6590,10 @@
         <v>268</v>
       </c>
       <c r="AO12">
-        <v>0.99889524579767786</v>
+        <v>0.99911949794866695</v>
       </c>
       <c r="AP12">
-        <v>20.253827042572624</v>
+        <v>16.142537607772773</v>
       </c>
       <c r="AR12" t="s">
         <v>210</v>
@@ -6694,16 +6694,16 @@
         <v>217</v>
       </c>
       <c r="Y13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Z13" t="s">
         <v>237</v>
       </c>
       <c r="AA13">
-        <v>0.99872710412225529</v>
+        <v>0.99924944940200633</v>
       </c>
       <c r="AB13">
-        <v>23.336424425319287</v>
+        <v>13.760094296550193</v>
       </c>
       <c r="AD13" t="s">
         <v>210</v>
@@ -6736,10 +6736,10 @@
         <v>270</v>
       </c>
       <c r="AO13">
-        <v>0.99635525152088078</v>
+        <v>0.99889524579767786</v>
       </c>
       <c r="AP13">
-        <v>66.820388783853375</v>
+        <v>20.253827042572624</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6804,16 +6804,16 @@
         <v>219</v>
       </c>
       <c r="Y14" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Z14" t="s">
         <v>238</v>
       </c>
       <c r="AA14">
-        <v>0.99710584239916322</v>
+        <v>0.99759397813724437</v>
       </c>
       <c r="AB14">
-        <v>53.059556015340199</v>
+        <v>44.110400817185507</v>
       </c>
       <c r="AD14" t="s">
         <v>210</v>
@@ -6846,10 +6846,10 @@
         <v>272</v>
       </c>
       <c r="AO14">
-        <v>0.99793473720944781</v>
+        <v>0.99806854175718718</v>
       </c>
       <c r="AP14">
-        <v>37.863151160123977</v>
+        <v>35.410067784902452</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6914,16 +6914,16 @@
         <v>221</v>
       </c>
       <c r="Y15" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Z15" t="s">
         <v>239</v>
       </c>
       <c r="AA15">
-        <v>0.99924944940200633</v>
+        <v>0.99890511709712682</v>
       </c>
       <c r="AB15">
-        <v>13.760094296550193</v>
+        <v>20.072853219340832</v>
       </c>
       <c r="AD15" t="s">
         <v>210</v>
@@ -7024,16 +7024,16 @@
         <v>223</v>
       </c>
       <c r="Y16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s">
         <v>240</v>
       </c>
       <c r="AA16">
-        <v>0.99914104512082091</v>
+        <v>0.9975822055979704</v>
       </c>
       <c r="AB16">
-        <v>15.747506118283479</v>
+        <v>44.326230703875503</v>
       </c>
       <c r="AD16" t="s">
         <v>210</v>
@@ -7134,16 +7134,16 @@
         <v>225</v>
       </c>
       <c r="Y17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z17" t="s">
         <v>241</v>
       </c>
       <c r="AA17">
-        <v>0.9976461542275985</v>
+        <v>0.99883020545500567</v>
       </c>
       <c r="AB17">
-        <v>43.153839160693863</v>
+        <v>21.446233324896248</v>
       </c>
       <c r="AD17" t="s">
         <v>210</v>
@@ -7244,16 +7244,16 @@
         <v>227</v>
       </c>
       <c r="Y18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s">
         <v>242</v>
       </c>
       <c r="AA18">
-        <v>0.99870476779891471</v>
+        <v>0.99872710412225529</v>
       </c>
       <c r="AB18">
-        <v>23.745923686563614</v>
+        <v>23.336424425319287</v>
       </c>
       <c r="AD18" t="s">
         <v>210</v>
@@ -7286,10 +7286,10 @@
         <v>280</v>
       </c>
       <c r="AO18">
-        <v>0.99806854175718718</v>
+        <v>0.99635525152088078</v>
       </c>
       <c r="AP18">
-        <v>35.410067784902452</v>
+        <v>66.820388783853375</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7354,16 +7354,16 @@
         <v>229</v>
       </c>
       <c r="Y19" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Z19" t="s">
         <v>243</v>
       </c>
       <c r="AA19">
-        <v>0.99759397813724437</v>
+        <v>0.99914104512082091</v>
       </c>
       <c r="AB19">
-        <v>44.110400817185507</v>
+        <v>15.747506118283479</v>
       </c>
       <c r="AD19" t="s">
         <v>210</v>
@@ -7464,16 +7464,16 @@
         <v>231</v>
       </c>
       <c r="Y20" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="Z20" t="s">
         <v>244</v>
       </c>
       <c r="AA20">
-        <v>0.99890511709712682</v>
+        <v>0.9976461542275985</v>
       </c>
       <c r="AB20">
-        <v>20.072853219340832</v>
+        <v>43.153839160693863</v>
       </c>
       <c r="AD20" t="s">
         <v>210</v>
@@ -7518,7 +7518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D34494-0E56-4497-BB26-325067F8E221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA67702D-8A6C-4B4E-90CD-4ACF5A4E04EB}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7630,7 +7630,7 @@
         <v>292</v>
       </c>
       <c r="K11" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="L11">
         <v>9.9944870858215555</v>
@@ -7698,7 +7698,7 @@
         <v>294</v>
       </c>
       <c r="K12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L12">
         <v>5.4764817961853396</v>
@@ -7801,7 +7801,7 @@
         <v>298</v>
       </c>
       <c r="K14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L14">
         <v>3.9432065697252274</v>
@@ -7871,7 +7871,7 @@
         <v>302</v>
       </c>
       <c r="K16" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="L16">
         <v>4.1115133977210352</v>
@@ -7976,7 +7976,7 @@
         <v>308</v>
       </c>
       <c r="K19" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="L19">
         <v>6.4642612617009894</v>
@@ -8026,7 +8026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED4C6F5-46E1-42B4-B063-8927587216F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F195D08-57D0-40E4-879F-325EEECB1681}">
   <dimension ref="B9:P64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9582,7 +9582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040F5773-FC6C-4D8B-91D8-43D9E0E03C51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2334F95A-03FB-42F0-9179-85C79BBDA261}">
   <dimension ref="B2:M35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ARE_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ARE_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1932886B-522A-4C60-A434-3BAC698D1E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AA721E-96A2-49DA-9F54-0E49ACC9C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="437">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1430,6 +1430,15 @@
   </si>
   <si>
     <t>e_AE10-400_ARE,e_AE11-400_ARE,e_AE13-400_ARE,e_AE14-400_ARE,e_AE18-220_ARE,e_AE18-400_ARE,e_AE19-220_ARE,e_AE19-400_ARE,e_AE2-400_ARE,e_AE25-400_ARE,e_AE27-400_ARE,e_AE3-400_ARE,e_AE30-400_ARE,e_AE31-220_ARE,e_AE33-220_ARE,e_AE33-400_ARE,e_AE34-220_ARE,e_AE35-220_ARE,e_AE36-220_ARE,e_AE39-220_ARE,e_AE4-400_ARE,e_AE5-400_ARE,e_AE8-400_ARE,e_w1264942732-220_ARE,e_w1264993337-400_ARE,e_w132159924-220_ARE,e_w132159930-220_ARE,e_w132517028-220_ARE,e_w1348312852-400_ARE,e_w173064712-400_ARE,e_w174871442-400_ARE,e_w181332757-400_ARE,e_w181332762-400_ARE,e_w181332765-220_ARE,e_w200057688-220_ARE,e_w200057688-400_ARE,e_w259874704-220_ARE,e_w259874704-400_ARE,e_w260963603-400_ARE,e_w29494113-400_ARE,e_w29495157-400_ARE,e_w29495366-400_ARE,e_w29497443-400_ARE,e_w301647038-220_ARE,e_w301647038-400_ARE,e_w301651304-400_ARE,e_w301690692-220_ARE,e_w301911494-400_ARE,e_w309146009-400_ARE,e_w354339381-220_ARE,e_w354339381-400_ARE,e_w359425700-400_ARE,e_w375827318-400_ARE,e_w385901993-400_ARE,e_w416954890-220_ARE,e_w416981962-400_ARE,e_w526194855-220_ARE,e_w526194855-400_ARE,e_w722968894-400_ARE,e_w801739686-400_ARE,e_w94816851-400_ARE,e_w94950807-400_ARE,e_w94950821-400_ARE,e_w94950847-400_ARE,e_w95046332-220_ARE,e_w95084771-220_ARE,e_w95084776-220_ARE,e_w95084793-220_ARE,e_w95084794-220_ARE,e_w95084799-220_ARE,e_w95084799-400_ARE</t>
+  </si>
+  <si>
+    <t>e_stargate</t>
+  </si>
+  <si>
+    <t>Stargate demand</t>
+  </si>
+  <si>
+    <t>elc_stargate</t>
   </si>
 </sst>
 </file>
@@ -1933,7 +1942,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2344,6 +2353,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -2743,7 +2753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B11:V28"/>
+  <dimension ref="B11:V29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -2753,7 +2763,7 @@
     <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.53125" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
@@ -3264,11 +3274,21 @@
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>434</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -3366,8 +3386,24 @@
         <v>433</v>
       </c>
     </row>
+    <row r="29" spans="2:22">
+      <c r="J29" t="str">
+        <f>C25</f>
+        <v>e_stargate</v>
+      </c>
+      <c r="K29" s="154" t="s">
+        <v>368</v>
+      </c>
+      <c r="L29" t="s">
+        <v>436</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
